--- a/config/yunying/reunion_recharge.xlsx
+++ b/config/yunying/reunion_recharge.xlsx
@@ -1,12 +1,12 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="27945" windowHeight="12375" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="reunion_recharge" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="reunion_recharge" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -1165,8 +1165,6 @@
           <t>-1</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1253,7 +1251,7 @@
       </c>
       <c r="D4" s="1" t="inlineStr">
         <is>
-          <t>復帰パック</t>
+          <t>回归包</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1320,7 +1318,7 @@
       </c>
       <c r="D5" s="1" t="inlineStr">
         <is>
-          <t>復帰パック</t>
+          <t>回归包</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1387,7 +1385,7 @@
       </c>
       <c r="D6" s="1" t="inlineStr">
         <is>
-          <t>復帰パック</t>
+          <t>回归包</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1454,7 +1452,7 @@
       </c>
       <c r="D7" s="1" t="inlineStr">
         <is>
-          <t>復帰パック</t>
+          <t>回归包</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1521,7 +1519,7 @@
       </c>
       <c r="D8" s="1" t="inlineStr">
         <is>
-          <t>復帰パック</t>
+          <t>回归包</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -1571,19 +1569,8 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr"/>
-      <c r="B9" t="inlineStr"/>
       <c r="C9" s="1" t="inlineStr"/>
       <c r="D9" s="1" t="inlineStr"/>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1603,7 +1590,7 @@
       </c>
       <c r="D10" s="1" t="inlineStr">
         <is>
-          <t>復帰パック</t>
+          <t>回归包</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -1670,7 +1657,7 @@
       </c>
       <c r="D11" s="1" t="inlineStr">
         <is>
-          <t>復帰パック</t>
+          <t>回归包</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1737,7 +1724,7 @@
       </c>
       <c r="D12" s="1" t="inlineStr">
         <is>
-          <t>復帰パック</t>
+          <t>回归包</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1804,7 +1791,7 @@
       </c>
       <c r="D13" s="1" t="inlineStr">
         <is>
-          <t>復帰パック</t>
+          <t>回归包</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1871,7 +1858,7 @@
       </c>
       <c r="D14" s="1" t="inlineStr">
         <is>
-          <t>復帰パック</t>
+          <t>回归包</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1921,19 +1908,8 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr"/>
-      <c r="B15" t="inlineStr"/>
       <c r="C15" s="1" t="inlineStr"/>
       <c r="D15" s="1" t="inlineStr"/>
-      <c r="E15" t="inlineStr"/>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr"/>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1953,7 +1929,7 @@
       </c>
       <c r="D16" s="1" t="inlineStr">
         <is>
-          <t>復帰パック</t>
+          <t>回归包</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -2020,7 +1996,7 @@
       </c>
       <c r="D17" s="1" t="inlineStr">
         <is>
-          <t>復帰パック</t>
+          <t>回归包</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -2087,7 +2063,7 @@
       </c>
       <c r="D18" s="1" t="inlineStr">
         <is>
-          <t>復帰パック</t>
+          <t>回归包</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -2154,7 +2130,7 @@
       </c>
       <c r="D19" s="1" t="inlineStr">
         <is>
-          <t>復帰パック</t>
+          <t>回归包</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -2221,7 +2197,7 @@
       </c>
       <c r="D20" s="1" t="inlineStr">
         <is>
-          <t>復帰パック</t>
+          <t>回归包</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -2271,19 +2247,8 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr"/>
-      <c r="B21" t="inlineStr"/>
       <c r="C21" s="1" t="inlineStr"/>
       <c r="D21" s="1" t="inlineStr"/>
-      <c r="E21" t="inlineStr"/>
-      <c r="F21" t="inlineStr"/>
-      <c r="G21" t="inlineStr"/>
-      <c r="H21" t="inlineStr"/>
-      <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2303,7 +2268,7 @@
       </c>
       <c r="D22" s="1" t="inlineStr">
         <is>
-          <t>復帰パック</t>
+          <t>回归包</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -2370,7 +2335,7 @@
       </c>
       <c r="D23" s="1" t="inlineStr">
         <is>
-          <t>復帰パック</t>
+          <t>回归包</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -2437,7 +2402,7 @@
       </c>
       <c r="D24" s="1" t="inlineStr">
         <is>
-          <t>復帰パック</t>
+          <t>回归包</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -2504,7 +2469,7 @@
       </c>
       <c r="D25" s="1" t="inlineStr">
         <is>
-          <t>復帰パック</t>
+          <t>回归包</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -2571,7 +2536,7 @@
       </c>
       <c r="D26" s="1" t="inlineStr">
         <is>
-          <t>復帰パック</t>
+          <t>回归包</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -2638,7 +2603,7 @@
       </c>
       <c r="D27" s="1" t="inlineStr">
         <is>
-          <t>復帰パック</t>
+          <t>回归包</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -2688,19 +2653,8 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" t="inlineStr"/>
-      <c r="B28" t="inlineStr"/>
       <c r="C28" s="1" t="inlineStr"/>
       <c r="D28" s="1" t="inlineStr"/>
-      <c r="E28" t="inlineStr"/>
-      <c r="F28" t="inlineStr"/>
-      <c r="G28" t="inlineStr"/>
-      <c r="H28" t="inlineStr"/>
-      <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -2720,7 +2674,7 @@
       </c>
       <c r="D29" s="1" t="inlineStr">
         <is>
-          <t>復帰パック</t>
+          <t>回归包</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -2787,7 +2741,7 @@
       </c>
       <c r="D30" s="1" t="inlineStr">
         <is>
-          <t>復帰パック</t>
+          <t>回归包</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -2854,7 +2808,7 @@
       </c>
       <c r="D31" s="1" t="inlineStr">
         <is>
-          <t>復帰パック</t>
+          <t>回归包</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -2921,7 +2875,7 @@
       </c>
       <c r="D32" s="1" t="inlineStr">
         <is>
-          <t>復帰パック</t>
+          <t>回归包</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -2988,7 +2942,7 @@
       </c>
       <c r="D33" s="1" t="inlineStr">
         <is>
-          <t>復帰パック</t>
+          <t>回归包</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -3055,7 +3009,7 @@
       </c>
       <c r="D34" s="1" t="inlineStr">
         <is>
-          <t>復帰パック</t>
+          <t>回归包</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -3105,19 +3059,8 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" t="inlineStr"/>
-      <c r="B35" t="inlineStr"/>
       <c r="C35" s="1" t="inlineStr"/>
       <c r="D35" s="1" t="inlineStr"/>
-      <c r="E35" t="inlineStr"/>
-      <c r="F35" t="inlineStr"/>
-      <c r="G35" t="inlineStr"/>
-      <c r="H35" t="inlineStr"/>
-      <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -3137,7 +3080,7 @@
       </c>
       <c r="D36" s="1" t="inlineStr">
         <is>
-          <t>復帰パック</t>
+          <t>回归包</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -3204,7 +3147,7 @@
       </c>
       <c r="D37" s="1" t="inlineStr">
         <is>
-          <t>復帰パック</t>
+          <t>回归包</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -3271,7 +3214,7 @@
       </c>
       <c r="D38" s="1" t="inlineStr">
         <is>
-          <t>復帰パック</t>
+          <t>回归包</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -3338,7 +3281,7 @@
       </c>
       <c r="D39" s="1" t="inlineStr">
         <is>
-          <t>復帰パック</t>
+          <t>回归包</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -3405,7 +3348,7 @@
       </c>
       <c r="D40" s="1" t="inlineStr">
         <is>
-          <t>復帰パック</t>
+          <t>回归包</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -3472,7 +3415,7 @@
       </c>
       <c r="D41" s="1" t="inlineStr">
         <is>
-          <t>復帰パック</t>
+          <t>回归包</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -3522,19 +3465,8 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" t="inlineStr"/>
-      <c r="B42" t="inlineStr"/>
       <c r="C42" s="1" t="inlineStr"/>
       <c r="D42" s="1" t="inlineStr"/>
-      <c r="E42" t="inlineStr"/>
-      <c r="F42" t="inlineStr"/>
-      <c r="G42" t="inlineStr"/>
-      <c r="H42" t="inlineStr"/>
-      <c r="I42" t="inlineStr"/>
-      <c r="J42" t="inlineStr"/>
-      <c r="K42" t="inlineStr"/>
-      <c r="L42" t="inlineStr"/>
-      <c r="M42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -3554,7 +3486,7 @@
       </c>
       <c r="D43" s="1" t="inlineStr">
         <is>
-          <t>復帰パック</t>
+          <t>回归包</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -3621,7 +3553,7 @@
       </c>
       <c r="D44" s="1" t="inlineStr">
         <is>
-          <t>復帰パック</t>
+          <t>回归包</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -3688,7 +3620,7 @@
       </c>
       <c r="D45" s="1" t="inlineStr">
         <is>
-          <t>復帰パック</t>
+          <t>回归包</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -3755,7 +3687,7 @@
       </c>
       <c r="D46" s="1" t="inlineStr">
         <is>
-          <t>復帰パック</t>
+          <t>回归包</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -3822,7 +3754,7 @@
       </c>
       <c r="D47" s="1" t="inlineStr">
         <is>
-          <t>復帰パック</t>
+          <t>回归包</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -3889,7 +3821,7 @@
       </c>
       <c r="D48" s="1" t="inlineStr">
         <is>
-          <t>復帰パック</t>
+          <t>回归包</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
